--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_aysen.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:46</t>
+    <t xml:space="preserve">2026-09-24 00:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -722,7 +722,7 @@
         <v>0.15</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +745,7 @@
         <v>0.04</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="11">
@@ -765,10 +765,10 @@
         <v>0.05</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="12">
@@ -995,7 +995,7 @@
         <v>0.14</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.01</v>
@@ -1038,13 +1038,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="24">
@@ -1251,7 +1251,7 @@
         <v>0.2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="33">
@@ -1271,10 +1271,10 @@
         <v>0.74</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="34">
@@ -1294,10 +1294,10 @@
         <v>-0.62</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-0.82</v>
+        <v>-0.81</v>
       </c>
     </row>
     <row r="35">
@@ -1317,10 +1317,10 @@
         <v>-0.71</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-0.84</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="36">
@@ -1527,7 +1527,7 @@
         <v>0.24</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="45">
@@ -1547,10 +1547,10 @@
         <v>-0.3</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="46">
@@ -1570,10 +1570,10 @@
         <v>-0.19</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="47">
@@ -1590,13 +1590,13 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="48">
@@ -1823,7 +1823,7 @@
         <v>0.09</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>0.27</v>
@@ -1849,7 +1849,7 @@
         <v>0.2</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="59">
@@ -1869,10 +1869,10 @@
         <v>0.15</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="60">
@@ -2122,7 +2122,7 @@
         <v>0.01</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>0.02</v>
@@ -2142,10 +2142,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F71" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>-0.01</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>0.01</v>
@@ -2352,7 +2352,7 @@
         <v>-0.36</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>-0.07</v>
@@ -2631,7 +2631,7 @@
         <v>-0.38</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="93">
@@ -2651,10 +2651,10 @@
         <v>0.22</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="94">
@@ -2694,10 +2694,10 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>-0.57</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_aysen.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:36</t>
+    <t xml:space="preserve">2026-10-01 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_aysen.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:08</t>
+    <t xml:space="preserve">2026-10-05 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
